--- a/GameConfig/Datas/Defines/__beans__.xlsx
+++ b/GameConfig/Datas/Defines/__beans__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -95,115 +95,73 @@
     <t>字段变体</t>
   </si>
   <si>
-    <t>item.ItemExchange</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>id</t>
+    <t>PassChapterCurrency</t>
+  </si>
+  <si>
+    <t>通关货币</t>
+  </si>
+  <si>
+    <t>章节通关货币奖励类型</t>
+  </si>
+  <si>
+    <t>CurrencyType</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>道具id</t>
-  </si>
-  <si>
-    <t>num</t>
-  </si>
-  <si>
-    <t>道具数量</t>
-  </si>
-  <si>
-    <t>test.TestExcelBean1</t>
-  </si>
-  <si>
-    <t>这是个测试excel结构</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>x2</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>黑色的</t>
-  </si>
-  <si>
-    <t>x3</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>x4</t>
+    <t>货币类型</t>
+  </si>
+  <si>
+    <t>BaseNum</t>
+  </si>
+  <si>
+    <t>基础值</t>
+  </si>
+  <si>
+    <t>ExtraNum</t>
+  </si>
+  <si>
+    <t>加成值</t>
+  </si>
+  <si>
+    <t>ChapterHangDropItem</t>
+  </si>
+  <si>
+    <t>挂机道具</t>
+  </si>
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>挂机道具类型</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Pos</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>test.TestExcelBean2</t>
-  </si>
-  <si>
-    <t>y1</t>
-  </si>
-  <si>
-    <t>y2</t>
-  </si>
-  <si>
-    <t>y3</t>
-  </si>
-  <si>
-    <t>test.Shape</t>
-  </si>
-  <si>
-    <t>test.Circle</t>
-  </si>
-  <si>
-    <t>Shape</t>
-  </si>
-  <si>
-    <t>圆</t>
-  </si>
-  <si>
-    <t>这是一个圆</t>
-  </si>
-  <si>
-    <t>radius</t>
-  </si>
-  <si>
-    <t>半径</t>
-  </si>
-  <si>
-    <t>test.Rectangle</t>
-  </si>
-  <si>
-    <t>矩形</t>
-  </si>
-  <si>
-    <t>这是一个矩形</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>宽度</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>高度</t>
+    <t>X轴</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Y轴</t>
   </si>
 </sst>
 </file>
@@ -819,17 +777,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="23" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyAlignment="1">
@@ -1154,14 +1106,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
+    <col min="3" max="4" width="20.625" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5089285714286" customWidth="1"/>
-    <col min="13" max="13" width="10.3839285714286" customWidth="1"/>
+    <col min="7" max="7" width="26.875" customWidth="1"/>
+    <col min="8" max="9" width="15" customWidth="1"/>
+    <col min="10" max="12" width="13.5083333333333" customWidth="1"/>
+    <col min="13" max="13" width="10.3833333333333" customWidth="1"/>
+    <col min="14" max="14" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1192,15 +1147,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
@@ -1257,220 +1212,102 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:16">
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="G4" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="J4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="L4" t="s">
         <v>26</v>
       </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" spans="10:14">
-      <c r="J5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="2" t="s">
+    <row r="5" spans="1:16">
+      <c r="J5" t="s">
         <v>28</v>
       </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="2:14">
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="6" spans="1:16">
+      <c r="J6" t="s">
         <v>30</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
         <v>31</v>
       </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" t="s">
         <v>32</v>
       </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="7" spans="10:14">
-      <c r="J7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
+    <row r="9" spans="1:16">
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="10:14">
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
-        <v>25</v>
-      </c>
-      <c r="N8" t="s">
-        <v>37</v>
+    <row r="11" spans="1:16">
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" spans="10:14">
-      <c r="J9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" t="s">
+    <row r="12" spans="1:16">
+      <c r="J12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="10:14">
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="10:14">
-      <c r="J12" t="s">
+      <c r="N12" t="s">
         <v>44</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Datas/Defines/__beans__.xlsx
+++ b/GameConfig/Datas/Defines/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -162,6 +162,75 @@
   </si>
   <si>
     <t>Y轴</t>
+  </si>
+  <si>
+    <t>AttrModifuerData</t>
+  </si>
+  <si>
+    <t>属性影响值</t>
+  </si>
+  <si>
+    <t>AttrType</t>
+  </si>
+  <si>
+    <t>属性类型</t>
+  </si>
+  <si>
+    <t>ModifyMode</t>
+  </si>
+  <si>
+    <t>byte</t>
+  </si>
+  <si>
+    <t>修正模式</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>修正值</t>
+  </si>
+  <si>
+    <t>WeaponModelBaseParam</t>
+  </si>
+  <si>
+    <t>武器模型偏移基础参数</t>
+  </si>
+  <si>
+    <t>OffsetX</t>
+  </si>
+  <si>
+    <t>偏移X</t>
+  </si>
+  <si>
+    <t>OffsetY</t>
+  </si>
+  <si>
+    <t>偏移Y</t>
+  </si>
+  <si>
+    <t>RotationX</t>
+  </si>
+  <si>
+    <t>旋转X</t>
+  </si>
+  <si>
+    <t>RotationY</t>
+  </si>
+  <si>
+    <t>旋转Y</t>
+  </si>
+  <si>
+    <t>RotationZ</t>
+  </si>
+  <si>
+    <t>旋转Z</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>缩放</t>
   </si>
 </sst>
 </file>
@@ -1106,12 +1175,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="31.125" customWidth="1"/>
     <col min="3" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
+    <col min="6" max="6" width="21.25" customWidth="1"/>
     <col min="7" max="7" width="26.875" customWidth="1"/>
     <col min="8" max="9" width="15" customWidth="1"/>
     <col min="10" max="12" width="13.5083333333333" customWidth="1"/>
@@ -1310,6 +1380,117 @@
         <v>44</v>
       </c>
     </row>
+    <row r="14" spans="1:16">
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="J16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="J20" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="J21" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="J22" t="s">
+        <v>64</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="J23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/GameConfig/Datas/Defines/__beans__.xlsx
+++ b/GameConfig/Datas/Defines/__beans__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\Defines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FB941A-CB36-4593-AF43-34869E488919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DF5AAA-C8D2-4442-9254-F040CDE2B2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -304,6 +304,10 @@
   </si>
   <si>
     <t>String类型引导参数2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -394,21 +398,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -690,394 +697,399 @@
   <dimension ref="A1:P31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.08203125" customWidth="1"/>
-    <col min="3" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="21.25" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.4140625" customWidth="1"/>
-    <col min="14" max="14" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="31.08203125" style="3" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="15" style="3" customWidth="1"/>
+    <col min="10" max="12" width="13.5" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.4140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J9" t="s">
+      <c r="J9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J10" t="s">
+      <c r="J10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N12" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J13" t="s">
+      <c r="J13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="3">
         <v>1</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N15" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J16" t="s">
+      <c r="J16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N18" t="s">
+      <c r="N18" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J19" t="s">
+      <c r="J19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N19" t="s">
+      <c r="N19" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J20" t="s">
+      <c r="J20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N20" t="s">
+      <c r="N20" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N22" t="s">
+      <c r="N22" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J23" t="s">
+      <c r="J23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N23" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J24" t="s">
+      <c r="J24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N24" t="s">
+      <c r="N24" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J25" t="s">
+      <c r="J25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N25" t="s">
+      <c r="N25" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J26" t="s">
+      <c r="J26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N26" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J27" t="s">
+      <c r="J27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N27" t="s">
+      <c r="N27" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="2:14" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:14" s="5" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="3">
         <v>1</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="H29" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="N29" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J30" s="3" t="s">
+      <c r="J30" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L30" s="3" t="s">
+      <c r="L30" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="N30" s="3" t="s">
+      <c r="N30" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J31" s="3" t="s">
+      <c r="J31" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="N31" s="3" t="s">
+      <c r="N31" s="4" t="s">
         <v>84</v>
       </c>
     </row>
